--- a/astro-site/public/dl/kit-gestion-personal/03-coste-laboral-mensual.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/03-coste-laboral-mensual.xlsx
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Nóminas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ratio Coste Laboral" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Previsión por Servicio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nóminas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratio Coste Laboral" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Previsión por Servicio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Nóminas'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt formatCode="€#,##0.00" numFmtId="164"/>
+    <numFmt numFmtId="164" formatCode="€#,##0.00"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -136,39 +138,39 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -528,15 +530,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -544,6 +547,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -579,9 +583,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -617,9 +619,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" t="inlineStr"/>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -648,8 +648,25 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -658,17 +675,17 @@
   <sheetPr>
     <tabColor rgb="002E7D32"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="22"/>
-    <col customWidth="1" max="2" min="2" width="18"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="18"/>
-    <col customWidth="1" max="6" min="6" width="16"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -685,6 +702,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1005,17 +1023,18 @@
       </c>
       <c r="C25" s="9">
         <f>SUM(C5:C24)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D25" s="9">
         <f>SUM(D5:D24)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E25" s="9">
         <f>SUM(E5:E24)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
@@ -1029,7 +1048,16 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A27:F27"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1038,14 +1066,14 @@
   <sheetPr>
     <tabColor rgb="001B5E20"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="30"/>
-    <col customWidth="1" max="2" min="2" width="22"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,6 +1090,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1078,7 +1107,7 @@
       </c>
       <c r="B5" s="13">
         <f>Nóminas!E25</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -1093,7 +1122,7 @@
       </c>
       <c r="B7" s="13">
         <f>IF(B4&gt;0,B5/B4*100,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -1106,11 +1135,13 @@
           <t>Semáforo:</t>
         </is>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="13" t="str">
         <f>IF(B7&lt;30,"🟢 EXCELENTE (&lt;30%)",IF(B7&lt;=35,"🟡 VIGILAR (30-35%)","🔴 ACCIÓN CORRECTIVA (&gt;35%)"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>🟢 EXCELENTE (&lt;30%)</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
@@ -1237,6 +1268,8 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
@@ -1250,7 +1283,16 @@
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1259,15 +1301,15 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="30"/>
-    <col customWidth="1" max="2" min="2" width="18"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1284,6 +1326,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1324,6 +1367,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
@@ -1339,7 +1383,7 @@
       </c>
       <c r="B10" s="17">
         <f>CEILING(B4/B5,1)</f>
-        <v/>
+        <v>4.0</v>
       </c>
     </row>
     <row r="11">
@@ -1350,7 +1394,7 @@
       </c>
       <c r="B11" s="17">
         <f>CEILING(B4/B6,1)</f>
-        <v/>
+        <v>7.0</v>
       </c>
     </row>
     <row r="12">
@@ -1361,7 +1405,7 @@
       </c>
       <c r="B12" s="17">
         <f>CEILING(B4/B7,1)</f>
-        <v/>
+        <v>4.0</v>
       </c>
     </row>
     <row r="13">
@@ -1372,9 +1416,10 @@
       </c>
       <c r="B13" s="17">
         <f>B10+B11+B12</f>
-        <v/>
-      </c>
-    </row>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
@@ -1393,9 +1438,11 @@
       </c>
       <c r="B16" s="9">
         <f>B13*B15*1.30</f>
-        <v/>
-      </c>
-    </row>
+        <v>35100.0</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
@@ -1409,6 +1456,15 @@
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-gestion-personal/03-coste-laboral-mensual.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/03-coste-laboral-mensual.xlsx
@@ -1,20 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nóminas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratio Coste Laboral" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Previsión por Servicio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Nóminas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ratio Coste Laboral" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Previsión por Servicio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Nóminas'!$4:$4</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="€#,##0.00"/>
+    <numFmt formatCode="€#,##0.00" numFmtId="164"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -138,39 +136,39 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="3" fontId="0" numFmtId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -530,16 +528,15 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="B2:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col customWidth="1" max="1" min="1" width="3"/>
+    <col customWidth="1" max="2" min="2" width="80"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -547,7 +544,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -583,7 +579,9 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="B9" t="inlineStr"/>
+    </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -619,7 +617,9 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
+    <row r="15">
+      <c r="B15" t="inlineStr"/>
+    </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -648,25 +648,8 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -675,17 +658,17 @@
   <sheetPr>
     <tabColor rgb="002E7D32"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col customWidth="1" max="1" min="1" width="22"/>
+    <col customWidth="1" max="2" min="2" width="18"/>
+    <col customWidth="1" max="3" min="3" width="18"/>
+    <col customWidth="1" max="4" min="4" width="16"/>
+    <col customWidth="1" max="5" min="5" width="18"/>
+    <col customWidth="1" max="6" min="6" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -702,7 +685,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1023,18 +1005,17 @@
       </c>
       <c r="C25" s="9">
         <f>SUM(C5:C24)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="D25" s="9">
         <f>SUM(D5:D24)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="E25" s="9">
         <f>SUM(E5:E24)</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="26"/>
+        <v/>
+      </c>
+    </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
@@ -1048,16 +1029,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A27:F27"/>
   </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -1066,14 +1038,14 @@
   <sheetPr>
     <tabColor rgb="001B5E20"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col customWidth="1" max="1" min="1" width="30"/>
+    <col customWidth="1" max="2" min="2" width="22"/>
+    <col customWidth="1" max="3" min="3" width="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1090,7 +1062,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1107,7 +1078,7 @@
       </c>
       <c r="B5" s="13">
         <f>Nóminas!E25</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1122,7 +1093,7 @@
       </c>
       <c r="B7" s="13">
         <f>IF(B4&gt;0,B5/B4*100,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1135,13 +1106,11 @@
           <t>Semáforo:</t>
         </is>
       </c>
-      <c r="B9" s="13" t="str">
+      <c r="B9" s="13">
         <f>IF(B7&lt;30,"🟢 EXCELENTE (&lt;30%)",IF(B7&lt;=35,"🟡 VIGILAR (30-35%)","🔴 ACCIÓN CORRECTIVA (&gt;35%)"))</f>
-        <v>🟢 EXCELENTE (&lt;30%)</v>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11"/>
+        <v/>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
@@ -1268,8 +1237,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
@@ -1283,16 +1250,7 @@
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -1301,15 +1259,15 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col customWidth="1" max="1" min="1" width="30"/>
+    <col customWidth="1" max="2" min="2" width="18"/>
+    <col customWidth="1" max="3" min="3" width="18"/>
+    <col customWidth="1" max="4" min="4" width="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1326,7 +1284,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1367,7 +1324,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
@@ -1383,7 +1339,7 @@
       </c>
       <c r="B10" s="17">
         <f>CEILING(B4/B5,1)</f>
-        <v>4.0</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1394,7 +1350,7 @@
       </c>
       <c r="B11" s="17">
         <f>CEILING(B4/B6,1)</f>
-        <v>7.0</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1405,7 +1361,7 @@
       </c>
       <c r="B12" s="17">
         <f>CEILING(B4/B7,1)</f>
-        <v>4.0</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1416,10 +1372,9 @@
       </c>
       <c r="B13" s="17">
         <f>B10+B11+B12</f>
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="14"/>
+        <v/>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
@@ -1438,11 +1393,9 @@
       </c>
       <c r="B16" s="9">
         <f>B13*B15*1.30</f>
-        <v>35100.0</v>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
+        <v/>
+      </c>
+    </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
@@ -1456,15 +1409,6 @@
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-gestion-personal/03-coste-laboral-mensual.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/03-coste-laboral-mensual.xlsx
@@ -13,7 +13,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Previsión por Servicio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Nóminas'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Nóminas'!$A$1:$I$37</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Ratio Coste Laboral'!$17:$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Ratio Coste Laboral'!$A$1:$E$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Previsión por Servicio'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,10 +26,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="€#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00 €"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,8 +101,40 @@
       <color rgb="00FFD700"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00888888"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -113,8 +153,23 @@
         <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECEFF1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -136,11 +191,55 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,6 +265,109 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="7" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -532,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -541,7 +743,7 @@
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>03 · Coste Laboral Mensual</t>
         </is>
@@ -549,110 +751,139 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla:</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>▸ Introduce los datos de nómina de cada empleado en la hoja 'Nóminas'.</t>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>▸ Vuelca los contratos en la hoja 'Nóminas': bruto mensual, número de pagas al año y horas contratadas por semana. Lo demás se calcula.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>▸ La Seguridad Social empresa (~30%) se calcula automáticamente.</t>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>▸ El tipo de cotización empresarial vive en UNA celda verde (C2 de 'Nóminas'), no dentro de las fórmulas: ajústalo a tu CNAE, a tu tipo de contrato y a tu convenio. El 33 % por defecto es lo que ronda un indefinido general sumando contingencias comunes, desempleo, AT/EP, FOGASA, formación profesional y MEI.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>▸ La hoja 'Ratio Coste Laboral' compara tu coste total con las ventas.</t>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>▸ Las pagas extra se PRORRATEAN: catorce pagas de 1.500 € no cuestan 1.500 € al mes, cuestan 1.750 €. La columna «Bruto prorrateado/mes» es la que hay que mirar para presupuestar.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>▸ La hoja 'Previsión por Servicio' te ayuda a planificar personal por turno.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>▸ La columna «Coste/hora» es el número que hay que llevar a la tarifa horaria del fichero 02: es coste real de empresa, no el bruto del convenio. Divide entre las SEMANAS EFECTIVAS (celda verde F2, 46,5 por defecto), no entre las 52 del calendario: las semanas de vacaciones y los festivos se pagan y no se trabajan, así que con 52 el coste por hora sale entre un 10 y un 13 % corto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>▸ En 'Ratio Coste Laboral', el coste del mes NO son sólo las nóminas: hay tres casillas verdes para las horas extra del mes (el total de la columna de coste del fichero 02), el personal externo o de ETT y otros costes de personal. Sin ellas el ratio sale por debajo del real y el semáforo aprueba de más.</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Ratios de referencia por tipo de negocio:</t>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>▸ La hoja 'Ratio Coste Laboral' compara ese coste con tus ventas netas del mes y lo juzga con los umbrales de TU tipo de negocio, elegido en la celda verde B3.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>▸ Fast casual / comida rápida: 25-28%</t>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>▸ La hoja 'Previsión por Servicio' dimensiona el equipo al revés: de cubiertos por servicio a plantilla necesaria en jornadas completas.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>▸ Restaurante casual: 28-33%</t>
-        </is>
-      </c>
+      <c r="B12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>▸ Fine dining / alta cocina: 35-40%</t>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>Lo que cambia respecto de la versión 1.1:</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>▸ Catering / eventos: 30-35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>▸ El semáforo ya no da «EXCELENTE» con la hoja en blanco: sin ventas Y sin coste no hay veredicto, y te dice cuál de los dos falta. Tampoco te felicita por un ratio absurdamente BAJO: por debajo del 60 % de tu objetivo avisa de que probablemente falten nóminas por volcar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>▸ Y ya no suspende a la alta cocina: un fine dining al 38 % está donde debe estar, y un fast casual al 38 % está en pérdidas. Los dos umbrales salen de la tabla de referencia de esa misma hoja, que ahora tiene los DIEZ tipos de negocio del BONUS-02 —hotel, pizzería, dark kitchen y heladería incluidos— con sus mismos umbrales: los dos ficheros no pueden dar veredictos distintos sobre el mismo ratio.</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Semáforo automático:</t>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>▸ La previsión de personal razona por SERVICIO. Ochenta cubiertos al día en dos servicios son cuarenta por servicio: dimensionar el turno con los ochenta duplicaba la plantilla.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>▸ 🟢 Verde: ratio &lt; 30% (excelente control)</t>
-        </is>
-      </c>
+      <c r="B17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>▸ 🟡 Amarillo: 30-35% (vigilar)</t>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Aviso: esto es una herramienta de gestión, no un cálculo de nómina. La cotización real depende de tu CNAE, del grupo de cotización, de las bonificaciones que te apliquen y del convenio. Contrástalo con tu gestoría antes de firmar nada.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>▸ 🔴 Rojo: &gt; 35% (acción correctiva necesaria)</t>
-        </is>
-      </c>
+      <c r="B19" s="3" t="n"/>
     </row>
     <row r="20"/>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
+      <c r="B21" s="3" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34">
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>Para editar una celda bloqueada: Revisar → Desproteger hoja (no tiene contraseña). Las celdas verdes ya son editables sin desproteger nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -677,15 +908,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -698,356 +932,885 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>Tipo de SS a cargo de la empresa (%):</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D2" t="str">
+        <f>"El coste total de cada empleado incluye un "&amp;TEXT($C$2,"0%")&amp;" de cotización empresarial sobre el bruto ya prorrateado"</f>
+        <v>El coste total de cada empleado incluye un 33% de cotización empresarial sobre el bruto ya prorrateado</v>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>Semanas efectivas al año:</t>
+        </is>
+      </c>
+      <c r="F2" s="25" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>AI Chef Pro · aichef.pro — Kit Gestión de Personal y Turnos</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>Empleado</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Puesto</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Salario Bruto Mes</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>SS Empresa (30%)</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Coste Total</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Horas Contratadas</t>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>Salario Bruto Mes (€)</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>Nº de pagas/año</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>Bruto prorrateado/mes (€)</t>
+        </is>
+      </c>
+      <c r="F4" s="26" t="inlineStr">
+        <is>
+          <t>Cotización SS empresa (€)</t>
+        </is>
+      </c>
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>Coste total/mes (€)</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="inlineStr">
+        <is>
+          <t>Horas contratadas/semana</t>
+        </is>
+      </c>
+      <c r="I4" s="27" t="inlineStr">
+        <is>
+          <t>Coste/hora (€)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="9">
-        <f>IF(C5&lt;&gt;"",C5*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E5" s="9">
-        <f>IF(C5&lt;&gt;"",C5+D5,"")</f>
-        <v/>
-      </c>
-      <c r="F5" s="7" t="n"/>
+      <c r="A5" s="28" t="n"/>
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E5" s="31">
+        <f>IF(OR($C5="",$D5=""),"",ROUND($C5*$D5/12,2))</f>
+        <v/>
+      </c>
+      <c r="F5" s="32">
+        <f>IF($E5="","",ROUND($E5*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G5" s="33">
+        <f>IF($E5="","",ROUND($E5+$F5,2))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34" t="n"/>
+      <c r="I5" s="33">
+        <f>IFERROR(IF(OR($G5="",$H5="",$H5=0,$F$2="",$F$2=0),"",ROUND($G5/($H5*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="9">
-        <f>IF(C6&lt;&gt;"",C6*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E6" s="9">
-        <f>IF(C6&lt;&gt;"",C6+D6,"")</f>
-        <v/>
-      </c>
-      <c r="F6" s="7" t="n"/>
+      <c r="A6" s="28" t="n"/>
+      <c r="B6" s="28" t="n"/>
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" s="31">
+        <f>IF(OR($C6="",$D6=""),"",ROUND($C6*$D6/12,2))</f>
+        <v/>
+      </c>
+      <c r="F6" s="32">
+        <f>IF($E6="","",ROUND($E6*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G6" s="33">
+        <f>IF($E6="","",ROUND($E6+$F6,2))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34" t="n"/>
+      <c r="I6" s="33">
+        <f>IFERROR(IF(OR($G6="",$H6="",$H6=0,$F$2="",$F$2=0),"",ROUND($G6/($H6*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="9">
-        <f>IF(C7&lt;&gt;"",C7*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E7" s="9">
-        <f>IF(C7&lt;&gt;"",C7+D7,"")</f>
-        <v/>
-      </c>
-      <c r="F7" s="7" t="n"/>
+      <c r="A7" s="28" t="n"/>
+      <c r="B7" s="28" t="n"/>
+      <c r="C7" s="29" t="n"/>
+      <c r="D7" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" s="31">
+        <f>IF(OR($C7="",$D7=""),"",ROUND($C7*$D7/12,2))</f>
+        <v/>
+      </c>
+      <c r="F7" s="32">
+        <f>IF($E7="","",ROUND($E7*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G7" s="33">
+        <f>IF($E7="","",ROUND($E7+$F7,2))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="33">
+        <f>IFERROR(IF(OR($G7="",$H7="",$H7=0,$F$2="",$F$2=0),"",ROUND($G7/($H7*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="9">
-        <f>IF(C8&lt;&gt;"",C8*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E8" s="9">
-        <f>IF(C8&lt;&gt;"",C8+D8,"")</f>
-        <v/>
-      </c>
-      <c r="F8" s="7" t="n"/>
+      <c r="A8" s="28" t="n"/>
+      <c r="B8" s="28" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" s="31">
+        <f>IF(OR($C8="",$D8=""),"",ROUND($C8*$D8/12,2))</f>
+        <v/>
+      </c>
+      <c r="F8" s="32">
+        <f>IF($E8="","",ROUND($E8*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G8" s="33">
+        <f>IF($E8="","",ROUND($E8+$F8,2))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34" t="n"/>
+      <c r="I8" s="33">
+        <f>IFERROR(IF(OR($G8="",$H8="",$H8=0,$F$2="",$F$2=0),"",ROUND($G8/($H8*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="9">
-        <f>IF(C9&lt;&gt;"",C9*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E9" s="9">
-        <f>IF(C9&lt;&gt;"",C9+D9,"")</f>
-        <v/>
-      </c>
-      <c r="F9" s="7" t="n"/>
+      <c r="A9" s="28" t="n"/>
+      <c r="B9" s="28" t="n"/>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E9" s="31">
+        <f>IF(OR($C9="",$D9=""),"",ROUND($C9*$D9/12,2))</f>
+        <v/>
+      </c>
+      <c r="F9" s="32">
+        <f>IF($E9="","",ROUND($E9*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G9" s="33">
+        <f>IF($E9="","",ROUND($E9+$F9,2))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="33">
+        <f>IFERROR(IF(OR($G9="",$H9="",$H9=0,$F$2="",$F$2=0),"",ROUND($G9/($H9*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="9">
-        <f>IF(C10&lt;&gt;"",C10*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E10" s="9">
-        <f>IF(C10&lt;&gt;"",C10+D10,"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="7" t="n"/>
+      <c r="A10" s="28" t="n"/>
+      <c r="B10" s="28" t="n"/>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E10" s="31">
+        <f>IF(OR($C10="",$D10=""),"",ROUND($C10*$D10/12,2))</f>
+        <v/>
+      </c>
+      <c r="F10" s="32">
+        <f>IF($E10="","",ROUND($E10*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G10" s="33">
+        <f>IF($E10="","",ROUND($E10+$F10,2))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34" t="n"/>
+      <c r="I10" s="33">
+        <f>IFERROR(IF(OR($G10="",$H10="",$H10=0,$F$2="",$F$2=0),"",ROUND($G10/($H10*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="9">
-        <f>IF(C11&lt;&gt;"",C11*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E11" s="9">
-        <f>IF(C11&lt;&gt;"",C11+D11,"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="7" t="n"/>
+      <c r="A11" s="28" t="n"/>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E11" s="31">
+        <f>IF(OR($C11="",$D11=""),"",ROUND($C11*$D11/12,2))</f>
+        <v/>
+      </c>
+      <c r="F11" s="32">
+        <f>IF($E11="","",ROUND($E11*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G11" s="33">
+        <f>IF($E11="","",ROUND($E11+$F11,2))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="33">
+        <f>IFERROR(IF(OR($G11="",$H11="",$H11=0,$F$2="",$F$2=0),"",ROUND($G11/($H11*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="9">
-        <f>IF(C12&lt;&gt;"",C12*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E12" s="9">
-        <f>IF(C12&lt;&gt;"",C12+D12,"")</f>
-        <v/>
-      </c>
-      <c r="F12" s="7" t="n"/>
+      <c r="A12" s="28" t="n"/>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E12" s="31">
+        <f>IF(OR($C12="",$D12=""),"",ROUND($C12*$D12/12,2))</f>
+        <v/>
+      </c>
+      <c r="F12" s="32">
+        <f>IF($E12="","",ROUND($E12*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G12" s="33">
+        <f>IF($E12="","",ROUND($E12+$F12,2))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34" t="n"/>
+      <c r="I12" s="33">
+        <f>IFERROR(IF(OR($G12="",$H12="",$H12=0,$F$2="",$F$2=0),"",ROUND($G12/($H12*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="9">
-        <f>IF(C13&lt;&gt;"",C13*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E13" s="9">
-        <f>IF(C13&lt;&gt;"",C13+D13,"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="7" t="n"/>
+      <c r="A13" s="28" t="n"/>
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E13" s="31">
+        <f>IF(OR($C13="",$D13=""),"",ROUND($C13*$D13/12,2))</f>
+        <v/>
+      </c>
+      <c r="F13" s="32">
+        <f>IF($E13="","",ROUND($E13*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G13" s="33">
+        <f>IF($E13="","",ROUND($E13+$F13,2))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34" t="n"/>
+      <c r="I13" s="33">
+        <f>IFERROR(IF(OR($G13="",$H13="",$H13=0,$F$2="",$F$2=0),"",ROUND($G13/($H13*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="9">
-        <f>IF(C14&lt;&gt;"",C14*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E14" s="9">
-        <f>IF(C14&lt;&gt;"",C14+D14,"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="7" t="n"/>
+      <c r="A14" s="28" t="n"/>
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E14" s="31">
+        <f>IF(OR($C14="",$D14=""),"",ROUND($C14*$D14/12,2))</f>
+        <v/>
+      </c>
+      <c r="F14" s="32">
+        <f>IF($E14="","",ROUND($E14*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G14" s="33">
+        <f>IF($E14="","",ROUND($E14+$F14,2))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34" t="n"/>
+      <c r="I14" s="33">
+        <f>IFERROR(IF(OR($G14="",$H14="",$H14=0,$F$2="",$F$2=0),"",ROUND($G14/($H14*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="9">
-        <f>IF(C15&lt;&gt;"",C15*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="9">
-        <f>IF(C15&lt;&gt;"",C15+D15,"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="7" t="n"/>
+      <c r="A15" s="28" t="n"/>
+      <c r="B15" s="28" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E15" s="31">
+        <f>IF(OR($C15="",$D15=""),"",ROUND($C15*$D15/12,2))</f>
+        <v/>
+      </c>
+      <c r="F15" s="32">
+        <f>IF($E15="","",ROUND($E15*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G15" s="33">
+        <f>IF($E15="","",ROUND($E15+$F15,2))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34" t="n"/>
+      <c r="I15" s="33">
+        <f>IFERROR(IF(OR($G15="",$H15="",$H15=0,$F$2="",$F$2=0),"",ROUND($G15/($H15*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="9">
-        <f>IF(C16&lt;&gt;"",C16*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="9">
-        <f>IF(C16&lt;&gt;"",C16+D16,"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="7" t="n"/>
+      <c r="A16" s="28" t="n"/>
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" s="31">
+        <f>IF(OR($C16="",$D16=""),"",ROUND($C16*$D16/12,2))</f>
+        <v/>
+      </c>
+      <c r="F16" s="32">
+        <f>IF($E16="","",ROUND($E16*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G16" s="33">
+        <f>IF($E16="","",ROUND($E16+$F16,2))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34" t="n"/>
+      <c r="I16" s="33">
+        <f>IFERROR(IF(OR($G16="",$H16="",$H16=0,$F$2="",$F$2=0),"",ROUND($G16/($H16*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="9">
-        <f>IF(C17&lt;&gt;"",C17*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="9">
-        <f>IF(C17&lt;&gt;"",C17+D17,"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="7" t="n"/>
+      <c r="A17" s="28" t="n"/>
+      <c r="B17" s="28" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E17" s="31">
+        <f>IF(OR($C17="",$D17=""),"",ROUND($C17*$D17/12,2))</f>
+        <v/>
+      </c>
+      <c r="F17" s="32">
+        <f>IF($E17="","",ROUND($E17*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G17" s="33">
+        <f>IF($E17="","",ROUND($E17+$F17,2))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34" t="n"/>
+      <c r="I17" s="33">
+        <f>IFERROR(IF(OR($G17="",$H17="",$H17=0,$F$2="",$F$2=0),"",ROUND($G17/($H17*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="9">
-        <f>IF(C18&lt;&gt;"",C18*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E18" s="9">
-        <f>IF(C18&lt;&gt;"",C18+D18,"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="7" t="n"/>
+      <c r="A18" s="28" t="n"/>
+      <c r="B18" s="28" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E18" s="31">
+        <f>IF(OR($C18="",$D18=""),"",ROUND($C18*$D18/12,2))</f>
+        <v/>
+      </c>
+      <c r="F18" s="32">
+        <f>IF($E18="","",ROUND($E18*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G18" s="33">
+        <f>IF($E18="","",ROUND($E18+$F18,2))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34" t="n"/>
+      <c r="I18" s="33">
+        <f>IFERROR(IF(OR($G18="",$H18="",$H18=0,$F$2="",$F$2=0),"",ROUND($G18/($H18*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="9">
-        <f>IF(C19&lt;&gt;"",C19*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E19" s="9">
-        <f>IF(C19&lt;&gt;"",C19+D19,"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="7" t="n"/>
+      <c r="A19" s="28" t="n"/>
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E19" s="31">
+        <f>IF(OR($C19="",$D19=""),"",ROUND($C19*$D19/12,2))</f>
+        <v/>
+      </c>
+      <c r="F19" s="32">
+        <f>IF($E19="","",ROUND($E19*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G19" s="33">
+        <f>IF($E19="","",ROUND($E19+$F19,2))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34" t="n"/>
+      <c r="I19" s="33">
+        <f>IFERROR(IF(OR($G19="",$H19="",$H19=0,$F$2="",$F$2=0),"",ROUND($G19/($H19*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="9">
-        <f>IF(C20&lt;&gt;"",C20*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E20" s="9">
-        <f>IF(C20&lt;&gt;"",C20+D20,"")</f>
-        <v/>
-      </c>
-      <c r="F20" s="7" t="n"/>
+      <c r="A20" s="28" t="n"/>
+      <c r="B20" s="28" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E20" s="31">
+        <f>IF(OR($C20="",$D20=""),"",ROUND($C20*$D20/12,2))</f>
+        <v/>
+      </c>
+      <c r="F20" s="32">
+        <f>IF($E20="","",ROUND($E20*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G20" s="33">
+        <f>IF($E20="","",ROUND($E20+$F20,2))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34" t="n"/>
+      <c r="I20" s="33">
+        <f>IFERROR(IF(OR($G20="",$H20="",$H20=0,$F$2="",$F$2=0),"",ROUND($G20/($H20*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="9">
-        <f>IF(C21&lt;&gt;"",C21*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E21" s="9">
-        <f>IF(C21&lt;&gt;"",C21+D21,"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="7" t="n"/>
+      <c r="A21" s="28" t="n"/>
+      <c r="B21" s="28" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E21" s="31">
+        <f>IF(OR($C21="",$D21=""),"",ROUND($C21*$D21/12,2))</f>
+        <v/>
+      </c>
+      <c r="F21" s="32">
+        <f>IF($E21="","",ROUND($E21*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G21" s="33">
+        <f>IF($E21="","",ROUND($E21+$F21,2))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34" t="n"/>
+      <c r="I21" s="33">
+        <f>IFERROR(IF(OR($G21="",$H21="",$H21=0,$F$2="",$F$2=0),"",ROUND($G21/($H21*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="9">
-        <f>IF(C22&lt;&gt;"",C22*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E22" s="9">
-        <f>IF(C22&lt;&gt;"",C22+D22,"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="7" t="n"/>
+      <c r="A22" s="28" t="n"/>
+      <c r="B22" s="28" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E22" s="31">
+        <f>IF(OR($C22="",$D22=""),"",ROUND($C22*$D22/12,2))</f>
+        <v/>
+      </c>
+      <c r="F22" s="32">
+        <f>IF($E22="","",ROUND($E22*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G22" s="33">
+        <f>IF($E22="","",ROUND($E22+$F22,2))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34" t="n"/>
+      <c r="I22" s="33">
+        <f>IFERROR(IF(OR($G22="",$H22="",$H22=0,$F$2="",$F$2=0),"",ROUND($G22/($H22*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="9">
-        <f>IF(C23&lt;&gt;"",C23*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E23" s="9">
-        <f>IF(C23&lt;&gt;"",C23+D23,"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="7" t="n"/>
+      <c r="A23" s="28" t="n"/>
+      <c r="B23" s="28" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E23" s="31">
+        <f>IF(OR($C23="",$D23=""),"",ROUND($C23*$D23/12,2))</f>
+        <v/>
+      </c>
+      <c r="F23" s="32">
+        <f>IF($E23="","",ROUND($E23*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G23" s="33">
+        <f>IF($E23="","",ROUND($E23+$F23,2))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34" t="n"/>
+      <c r="I23" s="33">
+        <f>IFERROR(IF(OR($G23="",$H23="",$H23=0,$F$2="",$F$2=0),"",ROUND($G23/($H23*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="9">
-        <f>IF(C24&lt;&gt;"",C24*0.30,"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="9">
-        <f>IF(C24&lt;&gt;"",C24+D24,"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="7" t="n"/>
+      <c r="A24" s="28" t="n"/>
+      <c r="B24" s="28" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E24" s="31">
+        <f>IF(OR($C24="",$D24=""),"",ROUND($C24*$D24/12,2))</f>
+        <v/>
+      </c>
+      <c r="F24" s="32">
+        <f>IF($E24="","",ROUND($E24*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G24" s="33">
+        <f>IF($E24="","",ROUND($E24+$F24,2))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34" t="n"/>
+      <c r="I24" s="33">
+        <f>IFERROR(IF(OR($G24="",$H24="",$H24=0,$F$2="",$F$2=0),"",ROUND($G24/($H24*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="28" t="n"/>
+      <c r="B25" s="28" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E25" s="31">
+        <f>IF(OR($C25="",$D25=""),"",ROUND($C25*$D25/12,2))</f>
+        <v/>
+      </c>
+      <c r="F25" s="32">
+        <f>IF($E25="","",ROUND($E25*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G25" s="33">
+        <f>IF($E25="","",ROUND($E25+$F25,2))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34" t="n"/>
+      <c r="I25" s="33">
+        <f>IFERROR(IF(OR($G25="",$H25="",$H25=0,$F$2="",$F$2=0),"",ROUND($G25/($H25*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="n"/>
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" s="31">
+        <f>IF(OR($C26="",$D26=""),"",ROUND($C26*$D26/12,2))</f>
+        <v/>
+      </c>
+      <c r="F26" s="32">
+        <f>IF($E26="","",ROUND($E26*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G26" s="33">
+        <f>IF($E26="","",ROUND($E26+$F26,2))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34" t="n"/>
+      <c r="I26" s="33">
+        <f>IFERROR(IF(OR($G26="",$H26="",$H26=0,$F$2="",$F$2=0),"",ROUND($G26/($H26*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="n"/>
+      <c r="B27" s="28" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E27" s="31">
+        <f>IF(OR($C27="",$D27=""),"",ROUND($C27*$D27/12,2))</f>
+        <v/>
+      </c>
+      <c r="F27" s="32">
+        <f>IF($E27="","",ROUND($E27*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G27" s="33">
+        <f>IF($E27="","",ROUND($E27+$F27,2))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34" t="n"/>
+      <c r="I27" s="33">
+        <f>IFERROR(IF(OR($G27="",$H27="",$H27=0,$F$2="",$F$2=0),"",ROUND($G27/($H27*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="n"/>
+      <c r="B28" s="28" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E28" s="31">
+        <f>IF(OR($C28="",$D28=""),"",ROUND($C28*$D28/12,2))</f>
+        <v/>
+      </c>
+      <c r="F28" s="32">
+        <f>IF($E28="","",ROUND($E28*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G28" s="33">
+        <f>IF($E28="","",ROUND($E28+$F28,2))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34" t="n"/>
+      <c r="I28" s="33">
+        <f>IFERROR(IF(OR($G28="",$H28="",$H28=0,$F$2="",$F$2=0),"",ROUND($G28/($H28*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="n"/>
+      <c r="B29" s="28" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E29" s="31">
+        <f>IF(OR($C29="",$D29=""),"",ROUND($C29*$D29/12,2))</f>
+        <v/>
+      </c>
+      <c r="F29" s="32">
+        <f>IF($E29="","",ROUND($E29*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G29" s="33">
+        <f>IF($E29="","",ROUND($E29+$F29,2))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34" t="n"/>
+      <c r="I29" s="33">
+        <f>IFERROR(IF(OR($G29="",$H29="",$H29=0,$F$2="",$F$2=0),"",ROUND($G29/($H29*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="n"/>
+      <c r="B30" s="28" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E30" s="31">
+        <f>IF(OR($C30="",$D30=""),"",ROUND($C30*$D30/12,2))</f>
+        <v/>
+      </c>
+      <c r="F30" s="32">
+        <f>IF($E30="","",ROUND($E30*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G30" s="33">
+        <f>IF($E30="","",ROUND($E30+$F30,2))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34" t="n"/>
+      <c r="I30" s="33">
+        <f>IFERROR(IF(OR($G30="",$H30="",$H30=0,$F$2="",$F$2=0),"",ROUND($G30/($H30*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="n"/>
+      <c r="B31" s="28" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E31" s="31">
+        <f>IF(OR($C31="",$D31=""),"",ROUND($C31*$D31/12,2))</f>
+        <v/>
+      </c>
+      <c r="F31" s="32">
+        <f>IF($E31="","",ROUND($E31*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G31" s="33">
+        <f>IF($E31="","",ROUND($E31+$F31,2))</f>
+        <v/>
+      </c>
+      <c r="H31" s="34" t="n"/>
+      <c r="I31" s="33">
+        <f>IFERROR(IF(OR($G31="",$H31="",$H31=0,$F$2="",$F$2=0),"",ROUND($G31/($H31*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="n"/>
+      <c r="B32" s="28" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E32" s="31">
+        <f>IF(OR($C32="",$D32=""),"",ROUND($C32*$D32/12,2))</f>
+        <v/>
+      </c>
+      <c r="F32" s="32">
+        <f>IF($E32="","",ROUND($E32*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G32" s="33">
+        <f>IF($E32="","",ROUND($E32+$F32,2))</f>
+        <v/>
+      </c>
+      <c r="H32" s="34" t="n"/>
+      <c r="I32" s="33">
+        <f>IFERROR(IF(OR($G32="",$H32="",$H32=0,$F$2="",$F$2=0),"",ROUND($G32/($H32*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E33" s="31">
+        <f>IF(OR($C33="",$D33=""),"",ROUND($C33*$D33/12,2))</f>
+        <v/>
+      </c>
+      <c r="F33" s="32">
+        <f>IF($E33="","",ROUND($E33*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G33" s="33">
+        <f>IF($E33="","",ROUND($E33+$F33,2))</f>
+        <v/>
+      </c>
+      <c r="H33" s="34" t="n"/>
+      <c r="I33" s="33">
+        <f>IFERROR(IF(OR($G33="",$H33="",$H33=0,$F$2="",$F$2=0),"",ROUND($G33/($H33*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="n"/>
+      <c r="B34" s="28" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E34" s="31">
+        <f>IF(OR($C34="",$D34=""),"",ROUND($C34*$D34/12,2))</f>
+        <v/>
+      </c>
+      <c r="F34" s="32">
+        <f>IF($E34="","",ROUND($E34*$C$2,2))</f>
+        <v/>
+      </c>
+      <c r="G34" s="33">
+        <f>IF($E34="","",ROUND($E34+$F34,2))</f>
+        <v/>
+      </c>
+      <c r="H34" s="34" t="n"/>
+      <c r="I34" s="33">
+        <f>IFERROR(IF(OR($G34="",$H34="",$H34=0,$F$2="",$F$2=0),"",ROUND($G34/($H34*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>TOTALES</t>
         </is>
       </c>
-      <c r="C25" s="9">
-        <f>SUM(C5:C24)</f>
+      <c r="C35" s="36">
+        <f>SUM($C$5:$C$34)</f>
         <v>0.0</v>
       </c>
-      <c r="D25" s="9">
-        <f>SUM(D5:D24)</f>
+      <c r="D35" s="37" t="n"/>
+      <c r="E35" s="36">
+        <f>SUM($E$5:$E$34)</f>
         <v>0.0</v>
       </c>
-      <c r="E25" s="9">
-        <f>SUM(E5:E24)</f>
+      <c r="F35" s="38">
+        <f>SUM($F$5:$F$34)</f>
         <v>0.0</v>
       </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="G35" s="38">
+        <f>SUM($G$5:$G$34)</f>
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="39">
+        <f>SUM($H$5:$H$34)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="38">
+        <f>IFERROR(IF(OR($G$35="",$H$35=0,$F$2="",$F$2=0),"",ROUND($G$35/($H$35*$F$2/12),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="40" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="C2" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2 · ss_empresa" prompt="Ajústalo a tu CNAE, contrato y convenio: un indefinido general ronda el 33-34 % sumando contingencias comunes, desempleo, AT/EP, FOGASA, FP y MEI."/>
+    <dataValidation sqref="F2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Semanas efectivas al año" error="Escribe un número mayor que cero." promptTitle="kitgp-v2b · Semanas efectivas al año" prompt="Las 52 del año MENOS las de vacaciones y festivos, que se pagan y no se trabajan: con 30 días naturales de vacaciones (art. 38 ET) y unos 14 festivos salen ~46,5. Es el divisor del «Coste/hora»: con 52 el coste por hora REALMENTE trabajada sale un 10-13 % corto, y ese número es el que se lleva a la tarifa del fichero 02." type="decimal" errorStyle="stop" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Número de pagas no válido" error="12, 14 o 15. La columna E prorratea el bruto anual a doce meses." promptTitle="kitgp-v2b · Número de pagas no válido" prompt="Doce pagas = extras prorrateadas mes a mes. Catorce (lo habitual en hostelería) o quince = las extras se pagan aparte, pero el coste mensual REAL sigue siendo el prorrateado: es lo que calcula la columna E." type="list" errorStyle="stop">
+      <formula1>"12,14,15"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1068,12 +1831,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1090,199 +1855,438 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tipo de negocio:</t>
+        </is>
+      </c>
+      <c r="B3" s="41" t="n"/>
+    </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Ventas Netas del Mes (€):</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n"/>
+      <c r="B4" s="42" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Coste Laboral Total (€):</t>
-        </is>
-      </c>
-      <c r="B5" s="13">
-        <f>Nóminas!E25</f>
+          <t>Nóminas del mes (€) — sale de la hoja «Nóminas»:</t>
+        </is>
+      </c>
+      <c r="B5" s="31">
+        <f>Nóminas!$G$35</f>
         <v>0.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr"/>
-      <c r="B6" s="13" t="inlineStr"/>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Horas extra del mes (€):</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
+          <t>Personal externo / ETT (€):</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Otros costes de personal (€):</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="44" t="inlineStr">
+        <is>
+          <t>COSTE LABORAL TOTAL DEL MES (€):</t>
+        </is>
+      </c>
+      <c r="B9" s="45">
+        <f>IF(COUNT($B$5:$B$8)=0,"",ROUND(SUM($B$5:$B$8),2))</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
           <t>RATIO COSTE LABORAL (%):</t>
         </is>
       </c>
-      <c r="B7" s="13">
-        <f>IF(B4&gt;0,B5/B4*100,0)</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr"/>
-      <c r="B8" s="13" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="B11" s="46">
+        <f>IFERROR(IF(OR($B$4="",$B$4&lt;=0,$B$9="",$B$9&lt;=0),"",ROUND($B$9/$B$4,4)),"")</f>
+        <v/>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ratio objetivo de tu tipo:</t>
+        </is>
+      </c>
+      <c r="D11" s="46">
+        <f>IFERROR(VLOOKUP($B$3,$A$18:$E$27,4,FALSE),0.3)</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Máximo aceptable de tu tipo:</t>
+        </is>
+      </c>
+      <c r="D12" s="46">
+        <f>IFERROR(VLOOKUP($B$3,$A$18:$E$27,5,FALSE),0.35)</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>Semáforo:</t>
         </is>
       </c>
-      <c r="B9" s="13" t="str">
-        <f>IF(B7&lt;30,"🟢 EXCELENTE (&lt;30%)",IF(B7&lt;=35,"🟡 VIGILAR (30-35%)","🔴 ACCIÓN CORRECTIVA (&gt;35%)"))</f>
-        <v>🟢 EXCELENTE (&lt;30%)</v>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="B13" s="48" t="str">
+        <f>IF(OR($B$4="",$B$4&lt;=0),"— introduce las VENTAS netas del mes (B4)",IF(OR($B$9="",$B$9&lt;=0),"— aún no hay coste: vuelca las nóminas en la hoja «Nóminas»",IF($B$11&lt;$D$11*0.6,"⚠ ratio implausible: revisa que estén TODAS las nóminas",IF($B$11&lt;$D$11,"🟢 EXCELENTE (por debajo de tu objetivo)",IF($B$11&lt;=$D$12,"🟡 VIGILAR (en el límite)","🔴 ACCIÓN CORRECTIVA")))))</f>
+        <v>— introduce las VENTAS netas del mes (B4)</v>
+      </c>
+      <c r="C13" s="49" t="n"/>
+      <c r="D13" s="49" t="n"/>
+      <c r="E13" s="50" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="51" t="inlineStr">
+        <is>
+          <t>▸ Sin tipo de negocio elegido el semáforo cae al 30 % / 35 % genérico. Y por debajo del 60 % de tu objetivo no te felicita: un coste laboral así de bajo casi siempre significa que faltan nóminas por volcar, no que vayas sobrado.</t>
+        </is>
+      </c>
+      <c r="B14" s="49" t="n"/>
+      <c r="C14" s="49" t="n"/>
+      <c r="D14" s="49" t="n"/>
+      <c r="E14" s="50" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="44" t="inlineStr">
         <is>
           <t>Ratios de Referencia por Tipo</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>Tipo de Negocio</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Ratio Objetivo</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>Rango Aceptable</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Fast Casual / Comida Rápida</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>25-28%</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>22-30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Restaurante Casual</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>28-33%</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>25-35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Fine Dining / Alta Cocina</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>35-40%</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>33-42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Catering / Eventos</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>30-35%</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>28-38%</t>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Objetivo % (núm.)</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>Aceptable % (núm.)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Cafetería / Brunch</t>
+          <t>Fast Casual / Comida Rápida</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>28-32%</t>
+          <t>25-28%</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>25-35%</t>
-        </is>
+          <t>22-30%</t>
+        </is>
+      </c>
+      <c r="D18" s="46" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E18" s="46" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Bar / Cocktails</t>
+          <t>Restaurante Casual</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>25-30%</t>
+          <t>28-33%</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>22-33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21"/>
+          <t>25-35%</t>
+        </is>
+      </c>
+      <c r="D19" s="46" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E19" s="46" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fine Dining / Alta Cocina</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>35-40%</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>33-42%</t>
+        </is>
+      </c>
+      <c r="D20" s="46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E20" s="46" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Catering / Eventos</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>30-35%</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>28-38%</t>
+        </is>
+      </c>
+      <c r="D21" s="46" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E21" s="46" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
+          <t>Cafetería / Brunch</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>28-32%</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>25-35%</t>
+        </is>
+      </c>
+      <c r="D22" s="46" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E22" s="46" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bar / Cocktails</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>25-30%</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>22-33%</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E23" s="46" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Pizzería</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>26-30%</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>24-32%</t>
+        </is>
+      </c>
+      <c r="D24" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E24" s="46" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Dark Kitchen / Delivery</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>22-28%</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>20-30%</t>
+        </is>
+      </c>
+      <c r="D25" s="46" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E25" s="46" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Hotel (restaurante)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>35-42%</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>33-44%</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E26" s="46" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Heladería / Obrador</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>25-30%</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>22-32%</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E27" s="46" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="52" t="inlineStr">
+        <is>
+          <t>▸ Las dos columnas numéricas son el extremo superior de los rangos de texto: es lo que lee el VLOOKUP del semáforo, para que la tabla y el veredicto no puedan contradecirse. Son los mismos diez tipos y los mismos umbrales que la hoja «Ratios por Tipo» del BONUS-02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="40" t="inlineStr">
+        <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="31"/>
+    <row r="32"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A1:C1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
+  <dataValidations count="4">
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Tipo de negocio no válido" error="Elige uno de los diez tipos de la tabla de referencia de abajo." promptTitle="kitgp-v2b · Tipo de negocio no válido" prompt="De aquí salen los dos umbrales del semáforo por VLOOKUP sobre la tabla de esta misma hoja. Son los mismos diez tipos y los mismos umbrales que la calculadora del BONUS-02: los dos ficheros no pueden dar veredictos distintos sobre el mismo ratio. Si lo dejas en blanco, el semáforo usa el 30 % / 35 % genérico." type="list" errorStyle="stop">
+      <formula1>"Fast Casual / Comida Rápida,Restaurante Casual,Fine Dining / Alta Cocina,Catering / Eventos,Cafetería / Brunch,Bar / Cocktails,Pizzería,Dark Kitchen / Delivery,Hotel (restaurante),Heladería / Obrador"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Horas extra del mes (€)" error="Escribe un número mayor que cero." promptTitle="kitgp-v2b · Horas extra del mes (€)" prompt="Cópialo de «Resumen Mensual»!G37 del fichero 02 (el total de la columna «Coste de las horas extra»). El kit lo calcula y hasta ahora no lo leía nadie, así que el ratio salía corto." type="decimal" errorStyle="stop" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Personal externo / ETT (€)" error="Escribe un número mayor que cero." promptTitle="kitgp-v2b · Personal externo / ETT (€)" prompt="Extras de fin de semana, ETT, personal de refuerzo del día pico (el que recomienda contratar el BONUS-02). Es coste laboral aunque no esté en tu nómina." type="decimal" errorStyle="stop" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Otros costes de personal (€)" error="Escribe un número mayor que cero." promptTitle="kitgp-v2b · Otros costes de personal (€)" prompt="Dietas, formación obligatoria, vestuario, transporte, comida de personal… lo que tu contabilidad impute a personal y no salga de las nóminas." type="decimal" errorStyle="stop" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1303,17 +2307,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="53" t="inlineStr">
         <is>
           <t>Previsión de Personal por Servicio</t>
         </is>
@@ -1326,136 +2332,283 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="54" t="inlineStr">
+        <is>
+          <t>ENTRADAS — edita sólo las celdas verdes</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="n"/>
+      <c r="C3" s="55" t="n"/>
+      <c r="D3" s="55" t="n"/>
+      <c r="E3" s="55" t="n"/>
+    </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Covers previstos / día:</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
+          <t>Cubiertos previstos / día:</t>
+        </is>
+      </c>
+      <c r="B4" s="56" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Ratio covers/cocinero:</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>20</v>
+          <t>Servicios al día (comida + cena):</t>
+        </is>
+      </c>
+      <c r="B5" s="56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Ratio covers/camarero:</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>12</v>
+          <t>Cubiertos por SERVICIO:</t>
+        </is>
+      </c>
+      <c r="B6" s="57">
+        <f>IFERROR(IF(OR($B$4="",$B$5="",$B$5=0),"",ROUND($B$4/$B$5,0)),"")</f>
+        <v>40.0</v>
+      </c>
+      <c r="C6" s="58" t="inlineStr">
+        <is>
+          <t>← es la cifra que dimensiona el turno, no los cubiertos del día</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Ratio covers/barman:</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
+          <t>Cubiertos por cocinero y servicio:</t>
+        </is>
+      </c>
+      <c r="B7" s="56" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cubiertos por camarero y servicio:</t>
+        </is>
+      </c>
+      <c r="B8" s="59" t="n">
+        <v>22</v>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PERSONAL NECESARIO POR TURNO</t>
-        </is>
+          <t>Cubiertos por persona de barra y servicio:</t>
+        </is>
+      </c>
+      <c r="B9" s="59" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Cocineros necesarios:</t>
-        </is>
-      </c>
-      <c r="B10" s="17">
-        <f>CEILING(B4/B5,1)</f>
-        <v>4.0</v>
+          <t>Horas efectivas por servicio:</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Camareros necesarios:</t>
-        </is>
-      </c>
-      <c r="B11" s="17">
-        <f>CEILING(B4/B6,1)</f>
-        <v>7.0</v>
+          <t>Días de apertura / semana:</t>
+        </is>
+      </c>
+      <c r="B11" s="60" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Barmans necesarios:</t>
-        </is>
-      </c>
-      <c r="B12" s="17">
-        <f>CEILING(B4/B7,1)</f>
-        <v>4.0</v>
+          <t>Jornada contratada (h/semana):</t>
+        </is>
+      </c>
+      <c r="B12" s="60" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>TOTAL personal/turno:</t>
-        </is>
-      </c>
-      <c r="B13" s="17">
-        <f>B10+B11+B12</f>
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>Factor de cobertura (vacaciones, bajas y descansos):</t>
+        </is>
+      </c>
+      <c r="B13" s="61" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Salario medio bruto (€/mes):</t>
+        </is>
+      </c>
+      <c r="B14" s="62" t="n">
+        <v>1500</v>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>Salario medio mensual (€):</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>1800</v>
+          <t>Nº de pagas / año:</t>
+        </is>
+      </c>
+      <c r="B15" s="56" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>Coste laboral estimado/mes (€):</t>
-        </is>
-      </c>
-      <c r="B16" s="9">
-        <f>B13*B15*1.30</f>
-        <v>35100.0</v>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
+          <t>Tipo de SS a cargo de la empresa (%):</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="54" t="inlineStr">
+        <is>
+          <t>RESULTADO — de cubiertos a plantilla</t>
+        </is>
+      </c>
+      <c r="B17" s="64" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="C17" s="64" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="D17" s="64" t="inlineStr">
+        <is>
+          <t>Barra</t>
+        </is>
+      </c>
+      <c r="E17" s="64" t="inlineStr">
+        <is>
+          <t>Total / servicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Personal por SERVICIO:</t>
+        </is>
+      </c>
+      <c r="B18" s="65">
+        <f>IFERROR(IF(OR($B$6="",$B$7="",$B$7=0),0,CEILING($B$6/$B$7,1)),0)</f>
+        <v>2.0</v>
+      </c>
+      <c r="C18" s="65">
+        <f>IFERROR(IF(OR($B$6="",$B$8="",$B$8=0),0,CEILING($B$6/$B$8,1)),0)</f>
+        <v>2.0</v>
+      </c>
+      <c r="D18" s="65">
+        <f>IFERROR(IF(OR($B$6="",$B$9="",$B$9=0),0,CEILING($B$6/$B$9,1)),0)</f>
+        <v>1.0</v>
+      </c>
+      <c r="E18" s="65">
+        <f>IF($B$6="","",$B$18+$C$18+$D$18)</f>
+        <v>5.0</v>
+      </c>
+    </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
+          <t>Presencias al día (personas × servicios):</t>
+        </is>
+      </c>
+      <c r="B19" s="65">
+        <f>IF(OR($E$18="",$B$5=""),"",$E$18*$B$5)</f>
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Horas de plantilla necesarias / semana:</t>
+        </is>
+      </c>
+      <c r="B20" s="65">
+        <f>IF(OR($B$19="",$B$10="",$B$11=""),"",$B$19*$B$10*$B$11)</f>
+        <v>240.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>Plantilla necesaria (FTE):</t>
+        </is>
+      </c>
+      <c r="B21" s="65">
+        <f>IFERROR(IF(OR($B$20="",$B$12="",$B$12=0),"",CEILING($B$20/$B$12*$B$13,1)),"")</f>
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Coste laboral estimado del equipo (€/mes):</t>
+        </is>
+      </c>
+      <c r="B22" s="33">
+        <f>IFERROR(IF(OR($B$21="",$B$14="",$B$15=""),"",ROUND($B$21*$B$14*$B$15/12*(1+$B$16),2)),"")</f>
+        <v>16292.5</v>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="52" t="inlineStr">
+        <is>
+          <t>▸ FTE = personas a jornada completa, no personas por turno: las 240 h/semana que salen por defecto son siete contratos de 40 h con el 15 % de cobertura de libranzas, vacaciones y bajas ya dentro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="52" t="inlineStr">
+        <is>
+          <t>▸ El coste es bruto de convenio × las pagas que elijas, prorrateado a doce meses y con la cotización empresarial encima. Para el coste REAL de tu equipo usa la hoja «Nóminas», que parte de tus contratos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="inlineStr">
+        <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A2:D2"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Servicios al día no válido" error="Elige 1, 2 o 3." promptTitle="kitgp-v2b · Servicios al día no válido" prompt="Uno (sólo comidas o sólo cenas), dos (comida y cena) o tres (desayuno, comida y cena). Es lo que reparte los cubiertos del día entre turnos: ochenta cubiertos en dos servicios son cuarenta por servicio, y el equipo se dimensiona con esos cuarenta." type="list" errorStyle="stop">
+      <formula1>"1,2,3"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
